--- a/rehearsals/blind-03/out-after-fixes/a1/a1.xlsx
+++ b/rehearsals/blind-03/out-after-fixes/a1/a1.xlsx
@@ -13,14 +13,16 @@
     <sheet name="Stages" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Date coverage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Relationships" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AD$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AE$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$145</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Relationships'!$A$1:$O$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD221"/>
+  <dimension ref="A1:AE221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -511,6 +513,7 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="50" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="50" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,6 +681,11 @@
           <t>Issues</t>
         </is>
       </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Relationships (curated links, their status; reached at the validated stage; documents not supplied)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -826,6 +834,7 @@
         </is>
       </c>
       <c r="AD5" s="4" t="inlineStr"/>
+      <c r="AE5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -974,6 +983,7 @@
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr"/>
+      <c r="AE6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1122,6 +1132,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1266,6 +1277,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1410,6 +1422,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1558,6 +1571,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1706,6 +1720,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1856,6 +1871,7 @@
         </is>
       </c>
       <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AE12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2006,6 +2022,7 @@
           <t>I-LCC-ISSUER</t>
         </is>
       </c>
+      <c r="AE13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2158,6 +2175,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2298,6 +2316,7 @@
         </is>
       </c>
       <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AE15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2446,6 +2465,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2590,6 +2610,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2740,6 +2761,11 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FORM-4C [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; &lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-FORM-4C</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2888,6 +2914,7 @@
           <t>I-READING-F4C; I-F4C-EXCLUSION</t>
         </is>
       </c>
+      <c r="AE19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3034,6 +3061,11 @@
       <c r="AD20" s="4" t="inlineStr">
         <is>
           <t>I-READING-F4C</t>
+        </is>
+      </c>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FORM-4C [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; &lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-FORM-4C</t>
         </is>
       </c>
     </row>
@@ -3178,6 +3210,7 @@
           <t>I-F4G-LETTERING</t>
         </is>
       </c>
+      <c r="AE21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3314,6 +3347,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3451,6 +3485,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3587,6 +3622,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3723,6 +3759,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3863,6 +3900,7 @@
         </is>
       </c>
       <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AE26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4003,6 +4041,7 @@
         </is>
       </c>
       <c r="AD27" s="4" t="inlineStr"/>
+      <c r="AE27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -4143,6 +4182,7 @@
         </is>
       </c>
       <c r="AD28" s="4" t="inlineStr"/>
+      <c r="AE28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4283,6 +4323,7 @@
         </is>
       </c>
       <c r="AD29" s="4" t="inlineStr"/>
+      <c r="AE29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4427,6 +4468,7 @@
         </is>
       </c>
       <c r="AD30" s="4" t="inlineStr"/>
+      <c r="AE30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4567,6 +4609,7 @@
         </is>
       </c>
       <c r="AD31" s="4" t="inlineStr"/>
+      <c r="AE31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4707,6 +4750,7 @@
         </is>
       </c>
       <c r="AD32" s="4" t="inlineStr"/>
+      <c r="AE32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4849,6 +4893,11 @@
       <c r="AD33" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT; I-READING-T24</t>
+        </is>
+      </c>
+      <c r="AE33" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
     </row>
@@ -4985,6 +5034,7 @@
           <t>I-NO-CONSEQUENCE; I-ADD03-OM-MEMBER; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -5119,6 +5169,7 @@
           <t>I-NO-CONSEQUENCE; I-ADD03-OM-MEMBER</t>
         </is>
       </c>
+      <c r="AE35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -5263,6 +5314,7 @@
           <t>I-ADD03-CONSENT-DATE; I-ADD03-OM-MEMBER; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -5399,6 +5451,7 @@
           <t>I-NO-CONSEQUENCE; I-ADD03-OM-MEMBER</t>
         </is>
       </c>
+      <c r="AE37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -5533,6 +5586,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5673,6 +5727,7 @@
           <t>I-F4C-EXCLUSION</t>
         </is>
       </c>
+      <c r="AE39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5813,6 +5868,7 @@
           <t>I-ADD03-F4C-UNDERTAKING; I-F4C-EXCLUSION</t>
         </is>
       </c>
+      <c r="AE40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5947,6 +6003,11 @@
         </is>
       </c>
       <c r="AD41" s="4" t="inlineStr"/>
+      <c r="AE41" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -6081,6 +6142,7 @@
           <t>I-NO-CONSEQUENCE; I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -6213,6 +6275,7 @@
           <t>I-F4G-NO; I-ADD03-F4G-ITEM7</t>
         </is>
       </c>
+      <c r="AE43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -6351,6 +6414,7 @@
         </is>
       </c>
       <c r="AD44" s="4" t="inlineStr"/>
+      <c r="AE44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -6485,6 +6549,11 @@
       <c r="AD45" s="4" t="inlineStr">
         <is>
           <t>I-NO-CONSEQUENCE; I-ADD03-Q15; I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="AE45" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER</t>
         </is>
       </c>
     </row>
@@ -6635,6 +6704,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -6775,6 +6845,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -6913,6 +6984,7 @@
           <t>I-NO-CONSEQUENCE; I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -7051,6 +7123,7 @@
           <t>I-VOL-IV-SCALE</t>
         </is>
       </c>
+      <c r="AE49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -7187,6 +7260,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -7323,6 +7397,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AE51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -7459,6 +7534,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -7607,6 +7683,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -7755,6 +7832,7 @@
           <t>I-VOL-I-ENV-B; I-VOL-I-ENV-A-PRICES; I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -7907,6 +7985,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -8047,6 +8126,7 @@
         </is>
       </c>
       <c r="AD56" s="4" t="inlineStr"/>
+      <c r="AE56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -8195,6 +8275,7 @@
         </is>
       </c>
       <c r="AD57" s="4" t="inlineStr"/>
+      <c r="AE57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -8339,6 +8420,7 @@
         </is>
       </c>
       <c r="AD58" s="4" t="inlineStr"/>
+      <c r="AE58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -8479,6 +8561,7 @@
         </is>
       </c>
       <c r="AD59" s="4" t="inlineStr"/>
+      <c r="AE59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -8623,6 +8706,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -8767,6 +8851,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -8915,6 +9000,7 @@
           <t>I-VOL-I-ENV-A-PRICES</t>
         </is>
       </c>
+      <c r="AE62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -9059,6 +9145,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-COPIES</t>
         </is>
       </c>
+      <c r="AE63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -9209,6 +9296,7 @@
           <t>I-VOL-I-FILE-NAMES</t>
         </is>
       </c>
+      <c r="AE64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -9357,6 +9445,7 @@
         </is>
       </c>
       <c r="AD65" s="4" t="inlineStr"/>
+      <c r="AE65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -9497,6 +9586,7 @@
         </is>
       </c>
       <c r="AD66" s="4" t="inlineStr"/>
+      <c r="AE66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -9645,6 +9735,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -9791,6 +9882,11 @@
       <c r="AD68" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="AE68" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-MULTIPLE-PARTICIPATION [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; &lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-MULTIPLE-PARTICIPATION</t>
         </is>
       </c>
     </row>
@@ -9937,6 +10033,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE69" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FIN-STANDING [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; &lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-FIN-STANDING</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -10081,6 +10182,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE70" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FIN-STANDING [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; &lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-FIN-STANDING</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -10227,6 +10333,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -10371,6 +10478,7 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -10519,6 +10627,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE73" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-INVESTMENT-LICENCE [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-INVESTMENT-LICENCE</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -10665,6 +10778,11 @@
       <c r="AD74" s="4" t="inlineStr">
         <is>
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="AE74" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-DEBARMENT [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-DEBARMENT</t>
         </is>
       </c>
     </row>
@@ -10829,6 +10947,7 @@
           <t>I-NO-CONSEQUENCE; I-F4G-LETTERING</t>
         </is>
       </c>
+      <c r="AE75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -10973,6 +11092,7 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -11121,6 +11241,7 @@
           <t>I-VOL-I-APPENDICES</t>
         </is>
       </c>
+      <c r="AE77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -11271,6 +11392,7 @@
           <t>I-VOL-I-ENV-A-PRICES; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -11421,6 +11543,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -11567,6 +11690,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -11711,6 +11835,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -11855,6 +11980,11 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE82" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-QUOTED-PRICE [confirmed feeds_calculation] from calc:availability-payment; REACHED at ADD-03 (confirmed dependency): from VOL-V:29.3 via REL-PAY-MECHANISM &gt; REL-PAY-QUOTED-PRICE; REACHED at ADD-03 (proposed relationship): from VOL-V:31.4 via REL-PAY-DEDUCTIONS &gt; REL-PAY-QUOTED-PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -11999,6 +12129,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-FILE-NAMES</t>
         </is>
       </c>
+      <c r="AE83" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FINANCIAL-MODEL [proposed depends_on] from calc:availability-payment; -&gt; REL-MODEL-FORM-4F [confirmed feeds_calculation] to VOL-IV-F4F-02; REACHED at ADD-03 (proposed relationship): from VOL-V:31.4 via REL-PAY-DEDUCTIONS &gt; REL-PAY-FINANCIAL-MODEL; REACHED at ADD-03 (proposed relationship): from VOL-V:29.3 via REL-PAY-MECHANISM &gt; REL-PAY-FINANCIAL-MODEL</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -12143,6 +12278,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -12287,6 +12423,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -12431,6 +12568,7 @@
         </is>
       </c>
       <c r="AD86" s="4" t="inlineStr"/>
+      <c r="AE86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -12575,6 +12713,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -12719,6 +12858,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE88" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FINANCING-ASSUMPTIONS [possible depends_on] from calc:availability-payment; REACHED at ADD-03 (possible impact): from VOL-V:31.4 via REL-PAY-DEDUCTIONS &gt; REL-PAY-FINANCING-ASSUMPTIONS; REACHED at ADD-03 (possible impact): from VOL-V:29.3 via REL-PAY-MECHANISM &gt; REL-PAY-FINANCING-ASSUMPTIONS</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -12863,6 +13007,7 @@
         </is>
       </c>
       <c r="AD89" s="4" t="inlineStr"/>
+      <c r="AE89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -13003,6 +13148,7 @@
         </is>
       </c>
       <c r="AD90" s="4" t="inlineStr"/>
+      <c r="AE90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -13143,6 +13289,7 @@
         </is>
       </c>
       <c r="AD91" s="4" t="inlineStr"/>
+      <c r="AE91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -13283,6 +13430,7 @@
         </is>
       </c>
       <c r="AD92" s="4" t="inlineStr"/>
+      <c r="AE92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -13423,6 +13571,7 @@
         </is>
       </c>
       <c r="AD93" s="4" t="inlineStr"/>
+      <c r="AE93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -13571,6 +13720,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -13715,6 +13865,7 @@
         </is>
       </c>
       <c r="AD95" s="4" t="inlineStr"/>
+      <c r="AE95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -13867,6 +14018,7 @@
           <t>I-VOL-I-BOND-LONGSTOP</t>
         </is>
       </c>
+      <c r="AE96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -14007,6 +14159,7 @@
         </is>
       </c>
       <c r="AD97" s="4" t="inlineStr"/>
+      <c r="AE97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -14151,6 +14304,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -14295,6 +14449,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -14435,6 +14590,7 @@
         </is>
       </c>
       <c r="AD100" s="4" t="inlineStr"/>
+      <c r="AE100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -14579,6 +14735,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -14719,6 +14876,7 @@
         </is>
       </c>
       <c r="AD102" s="4" t="inlineStr"/>
+      <c r="AE102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -14871,6 +15029,7 @@
         </is>
       </c>
       <c r="AD103" s="4" t="inlineStr"/>
+      <c r="AE103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -15011,6 +15170,7 @@
         </is>
       </c>
       <c r="AD104" s="4" t="inlineStr"/>
+      <c r="AE104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -15151,6 +15311,7 @@
         </is>
       </c>
       <c r="AD105" s="4" t="inlineStr"/>
+      <c r="AE105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -15291,6 +15452,7 @@
         </is>
       </c>
       <c r="AD106" s="4" t="inlineStr"/>
+      <c r="AE106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -15437,6 +15599,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE107" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed; REACHED at ADD-03 (confirmed dependency): from VOL-II:T2-4 via REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -15585,6 +15752,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AE108" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-03 (confirmed dependency): from VOL-II:T2-4 via REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -15729,6 +15901,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE109" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -15873,6 +16050,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE110" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -16017,6 +16199,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE111" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -16161,6 +16348,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE112" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -16305,6 +16497,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE113" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -16449,6 +16646,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE114" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -16593,6 +16795,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE115" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -16737,6 +16944,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE116" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -16881,6 +17093,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AE117" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -17023,6 +17240,11 @@
       <c r="AD118" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT; I-READING-T24</t>
+        </is>
+      </c>
+      <c r="AE118" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
     </row>
@@ -17183,6 +17405,11 @@
           <t>I-READING-T24; I-PERMIT</t>
         </is>
       </c>
+      <c r="AE119" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-PROCESS-DESIGN [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-03 (confirmed dependency): from VOL-II:T2-4 via REL-T24-PROCESS-DESIGN</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -17323,6 +17550,7 @@
         </is>
       </c>
       <c r="AD120" s="4" t="inlineStr"/>
+      <c r="AE120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -17463,6 +17691,7 @@
         </is>
       </c>
       <c r="AD121" s="4" t="inlineStr"/>
+      <c r="AE121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -17607,6 +17836,7 @@
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AE122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -17747,6 +17977,7 @@
         </is>
       </c>
       <c r="AD123" s="4" t="inlineStr"/>
+      <c r="AE123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -17887,6 +18118,7 @@
         </is>
       </c>
       <c r="AD124" s="4" t="inlineStr"/>
+      <c r="AE124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -18031,6 +18263,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -18175,6 +18408,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -18319,6 +18553,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -18459,6 +18694,7 @@
         </is>
       </c>
       <c r="AD128" s="4" t="inlineStr"/>
+      <c r="AE128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -18603,6 +18839,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -18743,6 +18980,7 @@
         </is>
       </c>
       <c r="AD130" s="4" t="inlineStr"/>
+      <c r="AE130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -18883,6 +19121,7 @@
         </is>
       </c>
       <c r="AD131" s="4" t="inlineStr"/>
+      <c r="AE131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -19027,6 +19266,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -19167,6 +19407,7 @@
         </is>
       </c>
       <c r="AD133" s="4" t="inlineStr"/>
+      <c r="AE133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -19311,6 +19552,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AE134" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-03 (confirmed dependency): from VOL-II:T2-4 via REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -19451,6 +19697,7 @@
         </is>
       </c>
       <c r="AD135" s="4" t="inlineStr"/>
+      <c r="AE135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -19591,6 +19838,7 @@
         </is>
       </c>
       <c r="AD136" s="4" t="inlineStr"/>
+      <c r="AE136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -19735,6 +19983,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -19881,6 +20130,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AE138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -20025,6 +20275,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AE139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -20165,6 +20416,7 @@
         </is>
       </c>
       <c r="AD140" s="4" t="inlineStr"/>
+      <c r="AE140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -20305,6 +20557,7 @@
         </is>
       </c>
       <c r="AD141" s="4" t="inlineStr"/>
+      <c r="AE141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -20449,6 +20702,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -20589,6 +20843,7 @@
         </is>
       </c>
       <c r="AD143" s="4" t="inlineStr"/>
+      <c r="AE143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -20729,6 +20984,7 @@
         </is>
       </c>
       <c r="AD144" s="4" t="inlineStr"/>
+      <c r="AE144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -20869,6 +21125,7 @@
         </is>
       </c>
       <c r="AD145" s="4" t="inlineStr"/>
+      <c r="AE145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -21009,6 +21266,7 @@
         </is>
       </c>
       <c r="AD146" s="4" t="inlineStr"/>
+      <c r="AE146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -21149,6 +21407,7 @@
         </is>
       </c>
       <c r="AD147" s="4" t="inlineStr"/>
+      <c r="AE147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -21289,6 +21548,7 @@
         </is>
       </c>
       <c r="AD148" s="4" t="inlineStr"/>
+      <c r="AE148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -21429,6 +21689,7 @@
         </is>
       </c>
       <c r="AD149" s="4" t="inlineStr"/>
+      <c r="AE149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -21573,6 +21834,7 @@
         </is>
       </c>
       <c r="AD150" s="4" t="inlineStr"/>
+      <c r="AE150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -21713,6 +21975,7 @@
         </is>
       </c>
       <c r="AD151" s="4" t="inlineStr"/>
+      <c r="AE151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -21853,6 +22116,7 @@
         </is>
       </c>
       <c r="AD152" s="4" t="inlineStr"/>
+      <c r="AE152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -21993,6 +22257,7 @@
         </is>
       </c>
       <c r="AD153" s="4" t="inlineStr"/>
+      <c r="AE153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -22141,6 +22406,11 @@
           <t>I-READING-T24; I-PERMIT</t>
         </is>
       </c>
+      <c r="AE154" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-RELIABILITY-RUN [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-03 (confirmed dependency): from VOL-II:T2-4 via REL-T24-RELIABILITY-RUN</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -22289,6 +22559,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -22429,6 +22700,7 @@
         </is>
       </c>
       <c r="AD156" s="4" t="inlineStr"/>
+      <c r="AE156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -22573,6 +22845,7 @@
         </is>
       </c>
       <c r="AD157" s="4" t="inlineStr"/>
+      <c r="AE157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -22713,6 +22986,7 @@
         </is>
       </c>
       <c r="AD158" s="4" t="inlineStr"/>
+      <c r="AE158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -22853,6 +23127,7 @@
         </is>
       </c>
       <c r="AD159" s="4" t="inlineStr"/>
+      <c r="AE159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -22993,6 +23268,7 @@
         </is>
       </c>
       <c r="AD160" s="4" t="inlineStr"/>
+      <c r="AE160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -23133,6 +23409,7 @@
         </is>
       </c>
       <c r="AD161" s="4" t="inlineStr"/>
+      <c r="AE161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -23281,6 +23558,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -23429,6 +23707,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -23573,6 +23852,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AE164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -23713,6 +23993,7 @@
         </is>
       </c>
       <c r="AD165" s="4" t="inlineStr"/>
+      <c r="AE165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -23857,6 +24138,7 @@
         </is>
       </c>
       <c r="AD166" s="4" t="inlineStr"/>
+      <c r="AE166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -24001,6 +24283,7 @@
         </is>
       </c>
       <c r="AD167" s="4" t="inlineStr"/>
+      <c r="AE167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -24141,6 +24424,7 @@
         </is>
       </c>
       <c r="AD168" s="4" t="inlineStr"/>
+      <c r="AE168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -24281,6 +24565,7 @@
         </is>
       </c>
       <c r="AD169" s="4" t="inlineStr"/>
+      <c r="AE169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -24429,6 +24714,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -24607,6 +24893,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AE171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -24751,6 +25038,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -24899,6 +25187,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -25043,6 +25332,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -25187,6 +25477,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -25331,6 +25622,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -25505,6 +25797,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-A-PRICES; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -25649,6 +25942,7 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -25793,6 +26087,11 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE179" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-MULTIPLE-PARTICIPATION [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; &lt;- REL-ADD03-OM-OPERATOR-MEMBER [confirmed member_scope] from VOL-I:8.8; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.8 via REL-ADD03-OM-OPERATOR-MEMBER; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-MULTIPLE-PARTICIPATION</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -25937,6 +26236,11 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AE180" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-DEBARMENT [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium; REACHED at ADD-03 (confirmed dependency): from VOL-I:8.1 via REL-MEMBER-DEBARMENT</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -26081,6 +26385,7 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -26247,6 +26552,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -26387,6 +26693,7 @@
         </is>
       </c>
       <c r="AD183" s="4" t="inlineStr"/>
+      <c r="AE183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -26527,6 +26834,7 @@
         </is>
       </c>
       <c r="AD184" s="4" t="inlineStr"/>
+      <c r="AE184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -26667,6 +26975,7 @@
         </is>
       </c>
       <c r="AD185" s="4" t="inlineStr"/>
+      <c r="AE185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -26807,6 +27116,7 @@
         </is>
       </c>
       <c r="AD186" s="4" t="inlineStr"/>
+      <c r="AE186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -26947,6 +27257,7 @@
         </is>
       </c>
       <c r="AD187" s="4" t="inlineStr"/>
+      <c r="AE187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -27087,6 +27398,7 @@
         </is>
       </c>
       <c r="AD188" s="4" t="inlineStr"/>
+      <c r="AE188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -27227,6 +27539,7 @@
         </is>
       </c>
       <c r="AD189" s="4" t="inlineStr"/>
+      <c r="AE189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -27389,6 +27702,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -27563,6 +27877,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AE191" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FORM-4F [confirmed feeds_calculation] from calc:availability-payment; REACHED at ADD-03 (confirmed dependency): from VOL-V:29.3 via REL-PAY-MECHANISM &gt; REL-PAY-FORM-4F; REACHED at ADD-03 (proposed relationship): from VOL-V:31.4 via REL-PAY-DEDUCTIONS &gt; REL-PAY-FORM-4F</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -27707,6 +28026,11 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AE192" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MODEL-FORM-4F [confirmed feeds_calculation] from VOL-I-10.3-01; REACHED at ADD-03 (proposed relationship): from VOL-V:31.4 via REL-PAY-DEDUCTIONS &gt; REL-PAY-FINANCIAL-MODEL &gt; REL-MODEL-FORM-4F; REACHED at ADD-03 (proposed relationship): from VOL-V:29.3 via REL-PAY-MECHANISM &gt; REL-PAY-FINANCIAL-MODEL &gt; REL-MODEL-FORM-4F</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -27855,6 +28179,7 @@
           <t>I-VOL-V-MISSING; I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -28003,6 +28328,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -28147,6 +28473,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -28295,6 +28622,7 @@
         </is>
       </c>
       <c r="AD196" s="4" t="inlineStr"/>
+      <c r="AE196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -28443,6 +28771,7 @@
         </is>
       </c>
       <c r="AD197" s="4" t="inlineStr"/>
+      <c r="AE197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -28583,6 +28912,7 @@
         </is>
       </c>
       <c r="AD198" s="4" t="inlineStr"/>
+      <c r="AE198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -28723,6 +29053,7 @@
         </is>
       </c>
       <c r="AD199" s="4" t="inlineStr"/>
+      <c r="AE199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -28863,6 +29194,7 @@
         </is>
       </c>
       <c r="AD200" s="4" t="inlineStr"/>
+      <c r="AE200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -29003,6 +29335,7 @@
         </is>
       </c>
       <c r="AD201" s="4" t="inlineStr"/>
+      <c r="AE201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -29143,6 +29476,7 @@
         </is>
       </c>
       <c r="AD202" s="4" t="inlineStr"/>
+      <c r="AE202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -29283,6 +29617,7 @@
         </is>
       </c>
       <c r="AD203" s="4" t="inlineStr"/>
+      <c r="AE203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -29423,6 +29758,7 @@
         </is>
       </c>
       <c r="AD204" s="4" t="inlineStr"/>
+      <c r="AE204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -29563,6 +29899,7 @@
         </is>
       </c>
       <c r="AD205" s="4" t="inlineStr"/>
+      <c r="AE205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -29721,6 +30058,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AE206" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-RAMP-UP-DEDUCTIONS [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-03 (confirmed dependency): from VOL-II:T2-4 via REL-T24-RAMP-UP-DEDUCTIONS</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -29865,6 +30207,7 @@
         </is>
       </c>
       <c r="AD207" s="4" t="inlineStr"/>
+      <c r="AE207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -30013,6 +30356,11 @@
           <t>I-VOL-V-MISSING; I-FLOWS</t>
         </is>
       </c>
+      <c r="AE208" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -30161,6 +30509,11 @@
           <t>I-READING-T24; I-PERMIT; I-VOL-V-MISSING</t>
         </is>
       </c>
+      <c r="AE209" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-UNAVAILABILITY [confirmed limit_applies] from VOL-II:T2-4; NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each; REACHED at ADD-03 (confirmed dependency): from VOL-II:T2-4 via REL-T24-UNAVAILABILITY</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -30307,6 +30660,11 @@
       <c r="AD210" s="4" t="inlineStr">
         <is>
           <t>I-VOL-III; I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="AE210" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
         </is>
       </c>
     </row>
@@ -30449,6 +30807,7 @@
         </is>
       </c>
       <c r="AD211" s="4" t="inlineStr"/>
+      <c r="AE211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -30589,6 +30948,7 @@
         </is>
       </c>
       <c r="AD212" s="4" t="inlineStr"/>
+      <c r="AE212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -30737,6 +31097,11 @@
           <t>I-VOL-V-PERSISTENT-BREACH</t>
         </is>
       </c>
+      <c r="AE213" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 11 (Project Company Events of Default) (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): cannot be established: whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -30885,6 +31250,7 @@
         </is>
       </c>
       <c r="AD214" s="4" t="inlineStr"/>
+      <c r="AE214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -31025,6 +31391,7 @@
         </is>
       </c>
       <c r="AD215" s="4" t="inlineStr"/>
+      <c r="AE215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -31171,6 +31538,11 @@
       <c r="AD216" s="4" t="inlineStr">
         <is>
           <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="AE216" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 11 (Project Company Events of Default) (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): cannot be established: which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
         </is>
       </c>
     </row>
@@ -31317,6 +31689,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -31457,6 +31830,7 @@
         </is>
       </c>
       <c r="AD218" s="4" t="inlineStr"/>
+      <c r="AE218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -31605,6 +31979,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AE219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -31745,6 +32120,7 @@
         </is>
       </c>
       <c r="AD220" s="4" t="inlineStr"/>
+      <c r="AE220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -31885,9 +32261,10 @@
         </is>
       </c>
       <c r="AD221" s="4" t="inlineStr"/>
+      <c r="AE221" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AD221"/>
+  <autoFilter ref="A4:AE221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37661,7 +38038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -38667,94 +39044,106 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
+          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
+          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>C31 (automatic)</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/Q4</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
+          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/AppA/para1</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
+          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
+          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
+          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C31 (automatic)</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -38763,12 +39152,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
+          <t>I-OP-ADD-01/Q4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
+          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -38787,12 +39176,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q7</t>
+          <t>I-OP-ADD-01/AppA/para1</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q7: follow-up only (clarification CQ-CONCESSION-TERM): Volume V is left unamended, so whether VOL-V 3.1 not listed in Form 4-E would be taken as accepted under the Volume V note, and how 'the term' in VOL-V 3.2 and 42.2 reads, remain; a legal and commercial question for people</t>
+          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -38811,12 +39200,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q11</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
+          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -38835,12 +39224,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/7.1</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
+          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -38859,12 +39248,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/cover/para3</t>
+          <t>I-OP-ADD-02/Q7</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/cover/para3: cover summary vs provisions (C28 reports it on A2): CONTRADICTED 'The closure of the Authority's offices does not affect any deadline under the RFP Documents.': 2.1-2.2 make Sunday 22 November 2026 a non-Working Day, so the VOL-I 5.2 cut-off moves from 12 to 11 November 2026 and 3.2 gives 19 November 2026, and Q17 sets a deadline on that day (C28 does not detect this one; I-ADD03-CLOSURE). OMITTED: the deletion of VOL-V 39.3 (6.2), the Ramp-Up payment change 90% -&gt; 85% (6.1), the notices of 3.3-3.4 and the 10% shareholding lock-in (3.1), the process-design obligation (5.2), the uncountersigned Form 4-G treated as not submitted (7.2), the new Form 4-G undertaking 7 and the new undertaking with its exclusion consequence in the substituted Form 4-C declaration (4.2). UNDERSTATED: 'responds to clarification requests 15 to 19' while Q15 amends the ADD-02 response 9 and Q17 sets a deadline. C28's three 'contradicted' findings on 'replaces the fourth declaration in Form 4-C' are artefacts of making that substitution as insert + delete under 4.1: that claim is accurate (I-ADD03-COVER)</t>
+          <t>ADD-02/Q7: follow-up only (clarification CQ-CONCESSION-TERM): Volume V is left unamended, so whether VOL-V 3.1 not listed in Form 4-E would be taken as accepted under the Volume V note, and how 'the term' in VOL-V 3.2 and 42.2 reads, remain; a legal and commercial question for people</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -38883,12 +39272,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/2.2</t>
+          <t>I-OP-ADD-02/Q11</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/2.2: the cover says 'The closure of the Authority's offices does not affect any deadline under the RFP Documents.'; read with VOL-I 2.4 as amended by 2.1 it does (VOL-I 5.2 cut-off, ADD-03 3.2), and ADD-03 Q17 sets a deadline on the closure day itself. The cover is never applied (see I-ADD03-COVER, CQ-ADD03-CLOSURE)</t>
+          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -38907,12 +39296,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/3.2</t>
+          <t>I-OP-ADD-02/7.1</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/3.2: ADD-03 Q17 gives the same application a fixed date, 'not later than Sunday 22 November 2026' (the notified closure day); read with 2.1/2.2, 3.2 gives Thursday 19 November 2026. The Addendum does not say which governs (I-ADD03-CONSENT-DATE, CQ-ADD03-CONSENT-DATE); the programme plans to the earlier date</t>
+          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -38931,12 +39320,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/4.3</t>
+          <t>I-OP-ADD-03/cover/para3</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/4.3: the convenience translation does not match the governing Arabic: the Arabic period is 'خلال ثلاثة أيام عمل' (three working days), the translation reads 'within three (3) days'. The Arabic governs (4.3, VOL-I 9.4); see I-ADD03-F4C-TRANSLATION</t>
+          <t>ADD-03/cover/para3: cover summary vs provisions (C28 reports it on A2): CONTRADICTED 'The closure of the Authority's offices does not affect any deadline under the RFP Documents.': 2.1-2.2 make Sunday 22 November 2026 a non-Working Day, so the VOL-I 5.2 cut-off moves from 12 to 11 November 2026 and 3.2 gives 19 November 2026, and Q17 sets a deadline on that day (C28 does not detect this one; I-ADD03-CLOSURE). OMITTED: the deletion of VOL-V 39.3 (6.2), the Ramp-Up payment change 90% -&gt; 85% (6.1), the notices of 3.3-3.4 and the 10% shareholding lock-in (3.1), the process-design obligation (5.2), the uncountersigned Form 4-G treated as not submitted (7.2), the new Form 4-G undertaking 7 and the new undertaking with its exclusion consequence in the substituted Form 4-C declaration (4.2). UNDERSTATED: 'responds to clarification requests 15 to 19' while Q15 amends the ADD-02 response 9 and Q17 sets a deadline. C28's three 'contradicted' findings on 'replaces the fourth declaration in Form 4-C' are artefacts of making that substitution as insert + delete under 4.1: that claim is accurate (I-ADD03-COVER)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -38955,12 +39344,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/5.1</t>
+          <t>I-OP-ADD-03/2.2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/5.1: VOL-II 2.4 and the Table 2-4 heading say the table is reproduced from the Environmental Permit, which prevails over the reproduction; the Addendum does not say whether the Permit itself now states 0.5 mg/l, and the Permit is not in the pack (open question I-T24-PERMIT stays open)</t>
+          <t>ADD-03/2.2: the cover says 'The closure of the Authority's offices does not affect any deadline under the RFP Documents.'; read with VOL-I 2.4 as amended by 2.1 it does (VOL-I 5.2 cut-off, ADD-03 3.2), and ADD-03 Q17 sets a deadline on the closure day itself. The cover is never applied (see I-ADD03-COVER, CQ-ADD03-CLOSURE)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -38979,12 +39368,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/6.2(b)</t>
+          <t>I-OP-ADD-03/3.2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/6.2(b): the cover summary mentions only the deletion of Volume V Clause 31.4, not 39.3 (I-ADD03-COVER)</t>
+          <t>ADD-03/3.2: ADD-03 Q17 gives the same application a fixed date, 'not later than Sunday 22 November 2026' (the notified closure day); read with 2.1/2.2, 3.2 gives Thursday 19 November 2026. The Addendum does not say which governs (I-ADD03-CONSENT-DATE, CQ-ADD03-CONSENT-DATE); the programme plans to the earlier date</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -39003,12 +39392,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/7.1</t>
+          <t>I-OP-ADD-03/4.3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/7.1: the new item 7 is not mentioned in Section 7.1 or on the cover (I-ADD03-COVER)</t>
+          <t>ADD-03/4.3: the convenience translation does not match the governing Arabic: the Arabic period is 'خلال ثلاثة أيام عمل' (three working days), the translation reads 'within three (3) days'. The Arabic governs (4.3, VOL-I 9.4); see I-ADD03-F4C-TRANSLATION</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -39027,12 +39416,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/Q15(b)</t>
+          <t>I-OP-ADD-03/5.1</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/Q15(b): a clarification answer turns the optional translation of VOL-I 9.4 into a requirement for members incorporated outside the Kingdom; no consequence of omission is stated</t>
+          <t>ADD-03/5.1: VOL-II 2.4 and the Table 2-4 heading say the table is reproduced from the Environmental Permit, which prevails over the reproduction; the Addendum does not say whether the Permit itself now states 0.5 mg/l, and the Permit is not in the pack (open question I-T24-PERMIT stays open)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -39051,12 +39440,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-03/Q17</t>
+          <t>I-OP-ADD-03/6.2(b)</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ADD-03/Q17: two deadlines for one application in the same Addendum: Q17 fixes Sunday 22 November 2026 (the day 2.2 notifies as an office closure, so not a Working Day); 3.2 gives four Working Days before the Proposal Due Date, Thursday 19 November 2026 with that day not counted. Not resolved here (I-ADD03-CONSENT-DATE, CQ-ADD03-CONSENT-DATE); the programme plans to the earlier date</t>
+          <t>ADD-03/6.2(b): the cover summary mentions only the deletion of Volume V Clause 31.4, not 39.3 (I-ADD03-COVER)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -39075,12 +39464,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-01</t>
+          <t>I-OP-ADD-03/7.1</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-03/7.1: the new item 7 is not mentioned in Section 7.1 or on the cover (I-ADD03-COVER)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -39090,7 +39479,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -39099,12 +39488,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-02</t>
+          <t>I-OP-ADD-03/Q15(b)</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-03/Q15(b): a clarification answer turns the optional translation of VOL-I 9.4 into a requirement for members incorporated outside the Kingdom; no consequence of omission is stated</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -39114,7 +39503,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -39123,12 +39512,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-03</t>
+          <t>I-OP-ADD-03/Q17</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>ADD-03's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 15 to 19', but ADD-03/Q15 adds text to ADD-02:Q9: 'Yes. The response to clarification request 9 in Addendum No. 2 is amended by adding at the end: ‘A member incorporated outside the Kingdom shall attach an English translation to its Form 4-C.’ The Arabic text of Form 4-C governs in accorda…'; [understated] 'responds to clarification requests 15 to 19', but ADD-03/Q15(b) adds an obligation (VOL-I:9.4): 'Yes. The response to clarification request 9 in Addendum No. 2 is amended by adding at the end: ‘A member incorporated outside the Kingdom shall attach an English translation to its Form 4-C.’ The Arabic text of Form 4-C governs in accorda…'; [understated] 'responds to clarification requests 15 to 19', but ADD-03/Q17 adds an obligation (VOL-I:8.1): 'Bidders are referred to Section 3 of this Addendum. An application for consent to the admission of the proposed O&amp;M Operator as a member of a Bidder shall be submitted through the Portal not later than Sunday 22 November 2026.'; [omitted] ADD-03/3.3 adds an obligation (ADD-03:3.2); the summary does not mention it: 'A Bidder that intends to apply under Section 3.2 shall notify the Authority of that intention through the Portal within five (5) Working Days of the date of this Addendum.'; [omitted] ADD-03/4.4 adds an obligation (VOL-I:9.4, VOL-IV:F4-C); the summary does not mention it: 'Each member of the Bidder shall give the fourth declaration as substituted. A Form 4-C that contains the fourth declaration as issued is not a properly executed Form 4-C for the purposes of Volume I Clause 9.4.'; [omitted] ADD-03/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-03/6.1 amends VOL-V:29.3; the summary does not mention it: 'In Volume V Clause 29.3, ‘ninety per cent (90%)’ is deleted and ‘eighty-five per cent (85%)’ is substituted. The duration of the Ramp-Up Period is unchanged.'; [omitted] ADD-03/6.2(b) deletes VOL-V:39.3; the summary does not mention it: 'Volume V Clause 31.4 is deleted in its entirety. Volume V Clause 39.3, which provides for termination for persistent breach in the circumstances described in Clause 31.4, is also deleted. The remaining Clauses of Volume V are not renumbere…'; [omitted] ADD-03/7.2 adds an obligation (ADD-02:7.2); the summary does not mention it: 'Section 7.2 of Addendum No. 2 applies to the reissued Form 4-G. A Form 4-G that is not countersigned by the proposed O&amp;M Operator shall be treated as not submitted.'; [contradicted] 'The closure of the Authority's offices does not affect any deadline under the RFP Documents', but CLARIFICATION-CUTOFF (row VOL-I-5.2-01, VOL-I 5.2) moves from 2026-11-12 to 2026-11-11. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-03/Q17: two deadlines for one application in the same Addendum: Q17 fixes Sunday 22 November 2026 (the day 2.2 notifies as an office closure, so not a Working Day); 3.2 gives four Working Days before the Proposal Due Date, Thursday 19 November 2026 with that day not counted. Not resolved here (I-ADD03-CONSENT-DATE, CQ-ADD03-CONSENT-DATE); the programme plans to the earlier date</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -39138,7 +39527,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -39147,12 +39536,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, INTENT-NOTICE, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -39162,7 +39551,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>C28 (automatic)</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -39171,96 +39560,84 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 19 WD (total float -19 WD: latest start 2026-10-05 is before the planning date 2026-11-01; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-AUTO-SUMMARY-ADD-03</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 19 WD (total float -19 WD: latest start 2026-10-12 is before the planning date 2026-11-01; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>ADD-03's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 15 to 19', but ADD-03/Q15 adds text to ADD-02:Q9: 'Yes. The response to clarification request 9 in Addendum No. 2 is amended by adding at the end: ‘A member incorporated outside the Kingdom shall attach an English translation to its Form 4-C.’ The Arabic text of Form 4-C governs in accorda…'; [understated] 'responds to clarification requests 15 to 19', but ADD-03/Q15(b) adds an obligation (VOL-I:9.4): 'Yes. The response to clarification request 9 in Addendum No. 2 is amended by adding at the end: ‘A member incorporated outside the Kingdom shall attach an English translation to its Form 4-C.’ The Arabic text of Form 4-C governs in accorda…'; [understated] 'responds to clarification requests 15 to 19', but ADD-03/Q17 adds an obligation (VOL-I:8.1): 'Bidders are referred to Section 3 of this Addendum. An application for consent to the admission of the proposed O&amp;M Operator as a member of a Bidder shall be submitted through the Portal not later than Sunday 22 November 2026.'; [omitted] ADD-03/3.3 adds an obligation (ADD-03:3.2); the summary does not mention it: 'A Bidder that intends to apply under Section 3.2 shall notify the Authority of that intention through the Portal within five (5) Working Days of the date of this Addendum.'; [omitted] ADD-03/4.4 adds an obligation (VOL-I:9.4, VOL-IV:F4-C); the summary does not mention it: 'Each member of the Bidder shall give the fourth declaration as substituted. A Form 4-C that contains the fourth declaration as issued is not a properly executed Form 4-C for the purposes of Volume I Clause 9.4.'; [omitted] ADD-03/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-03/6.1 amends VOL-V:29.3; the summary does not mention it: 'In Volume V Clause 29.3, ‘ninety per cent (90%)’ is deleted and ‘eighty-five per cent (85%)’ is substituted. The duration of the Ramp-Up Period is unchanged.'; [omitted] ADD-03/6.2(b) deletes VOL-V:39.3; the summary does not mention it: 'Volume V Clause 31.4 is deleted in its entirety. Volume V Clause 39.3, which provides for termination for persistent breach in the circumstances described in Clause 31.4, is also deleted. The remaining Clauses of Volume V are not renumbere…'; [omitted] ADD-03/7.2 adds an obligation (ADD-02:7.2); the summary does not mention it: 'Section 7.2 of Addendum No. 2 applies to the reissued Form 4-G. A Form 4-G that is not countersigned by the proposed O&amp;M Operator shall be treated as not submitted.'; [contradicted] 'The closure of the Authority's offices does not affect any deadline under the RFP Documents', but CLARIFICATION-CUTOFF (row VOL-I-5.2-01, VOL-I 5.2) moves from 2026-11-12 to 2026-11-11. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-11-01; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, INTENT-NOTICE, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>I-A5-fin-model-build</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>A5 fin-model-build: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-25 is before the planning date 2026-11-01; not compressed) (VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 15 WD is an ASSUMPTION: fin_model_build)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 19 WD (total float -19 WD: latest start 2026-10-05 is before the planning date 2026-11-01; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -39275,7 +39652,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -39283,12 +39660,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>I-A5-model-auditor-appoint</t>
+          <t>I-A5-lcc-certificate</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>A5 model-auditor-appoint: INFEASIBLE by 4 WD (total float -4 WD: latest start 2026-10-26 is before the planning date 2026-11-01; not compressed) (VOL-I-10.3-02; duration 5 WD is an ASSUMPTION: model_auditor_appointment)</t>
+          <t>A5 lcc-certificate: INFEASIBLE by 19 WD (total float -19 WD: latest start 2026-10-12 is before the planning date 2026-11-01; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -39303,7 +39680,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.3-02</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
@@ -39311,17 +39688,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>I-A5-pcg-wording</t>
+          <t>I-A5-attendance-notice</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>A5 pcg-wording: INFEASIBLE by 4 WD (total float -4 WD: latest start 2026-10-26 is before the planning date 2026-11-01; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_wording)</t>
+          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-11-01; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Bid management</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -39331,7 +39708,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.7-01; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08</t>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -39339,17 +39716,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>I-A5-technical-proposal</t>
+          <t>I-A5-fin-model-build</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>A5 technical-proposal: INFEASIBLE by 4 WD (total float -4 WD: latest start 2026-10-26 is before the planning date 2026-11-01; not compressed) (ADD-02-5.2-01, ADD-02-T1-1-N3-01, ADD-03-5.2-01, VOL-I-11.3-01, VOL-I-9.2-01, VOL-I-9.7-01, VOL-I-T1-1-A, VOL-I-T1-1-B, VOL-I-T1-1-C, VOL-I-T1-1-D, VOL-I-T1-1-E, VOL-I-T1-1-F, VOL-II-1.1-01, VOL-II-1.2-01, VOL-II-1.3-01, VOL-II-1.4-01, VOL-II-2.1-01, VOL-II-2.2-01, VOL-II-2.2-02, VOL-II-2.3-01, VOL-II-2.4-01, VOL-II-2.5-01, VOL-II-3.1-01, VOL-II-3.2-01, VOL-II-3.2-02, VOL-II-3.3-01, VOL-II-3.4-01, VOL-II-3.5-01, VOL-II-4.1-01, VOL-II-4.3-01, VOL-II-4.3-02, VOL-II-4.4-01, VOL-II-4.4-02, VOL-II-4.5-01, VOL-II-5.1-01, VOL-II-5.2-01, VOL-II-5.2-02, VOL-II-5.3-01, VOL-II-5.3-02, VOL-II-5.4-01, VOL-II-5.4-02, VOL-II-5.5-01, VOL-II-5.5-02, VOL-II-6.1-01, VOL-II-6.1-02, VOL-II-6.2-01, VOL-II-6.3-01, VOL-II-6.3-02, VOL-II-6.4-01, VOL-II-6.4-02, VOL-II-7.1-01, VOL-II-7.2-01, VOL-II-7.4-01, VOL-II-8.1-01, VOL-II-8.2-01, VOL-II-8.3-01, VOL-II-8.3-02, VOL-II-8.4-01, VOL-II-8.4-02, VOL-II-8.5-01, VOL-II-8.5-02, VOL-II-9.1-01, VOL-II-9.1-02, VOL-II-9.2-01, VOL-II-9.3-01, VOL-II-9.4-01, VOL-II-9.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-II-T2-6-1, VOL-II-T2-6-2, VOL-II-T2-6-3, VOL-II-T2-6-4, VOL-II-T2-6-5, VOL-II-T2-6-6; duration 20 WD is an ASSUMPTION: technical_proposal)</t>
+          <t>A5 fin-model-build: INFEASIBLE by 5 WD (total float -5 WD: latest start 2026-10-25 is before the planning date 2026-11-01; not compressed) (VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 15 WD is an ASSUMPTION: fin_model_build)</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -39359,7 +39736,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>ADD-02-5.2-01; ADD-02-T1-1-N3-01; ADD-03-5.2-01; VOL-I-11.3-01; VOL-I-9.2-01; VOL-I-9.7-01; VOL-I-T1-1-A; VOL-I-T1-1-B; VOL-I-T1-1-C; VOL-I-T1-1-D; VOL-I-T1-1-E; VOL-I-T1-1-F; VOL-II-1.1-01; VOL-II-1.2-01; VOL-II-1.3-01; VOL-II-1.4-01; VOL-II-2.1-01; VOL-II-2.2-01; VOL-II-2.2-02; VOL-II-2.3-01; VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-3.1-01; VOL-II-3.2-01; VOL-II-3.2-02; VOL-II-3.3-01; VOL-II-3.4-01; VOL-II-3.5-01; VOL-II-4.1-01; VOL-II-4.3-01; VOL-II-4.3-02; VOL-II-4.4-01; VOL-II-4.4-02; VOL-II-4.5-01; VOL-II-5.1-01; VOL-II-5.2-01; VOL-II-5.2-02; VOL-II-5.3-01; VOL-II-5.3-02; VOL-II-5.4-01; VOL-II-5.4-02; VOL-II-5.5-01; VOL-II-5.5-02; VOL-II-6.1-01; VOL-II-6.1-02; VOL-II-6.2-01; VOL-II-6.3-01; VOL-II-6.3-02; VOL-II-6.4-01; VOL-II-6.4-02; VOL-II-7.1-01; VOL-II-7.2-01; VOL-II-7.4-01; VOL-II-8.1-01; VOL-II-8.2-01; VOL-II-8.3-01; VOL-II-8.3-02; VOL-II-8.4-01; VOL-II-8.4-02; VOL-II-8.5-01; VOL-II-8.5-02; VOL-II-9.1-01; VOL-II-9.1-02; VOL-II-9.2-01; VOL-II-9.3-01; VOL-II-9.4-01; VOL-II-9.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-3; VOL-II-T2-6-4; VOL-II-T2-6-5; VOL-II-T2-6-6</t>
+          <t>VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -39367,12 +39744,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>I-A5-model-audit-review</t>
+          <t>I-A5-model-auditor-appoint</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>A5 model-audit-review: INFEASIBLE by 4 WD (total float -4 WD: earliest start 2026-11-08 (after model-auditor-appoint) is after the latest start 2026-11-02; not compressed) (VOL-I-10.3-02; duration 10 WD is an ASSUMPTION: model_audit_review)</t>
+          <t>A5 model-auditor-appoint: INFEASIBLE by 4 WD (total float -4 WD: latest start 2026-10-26 is before the planning date 2026-11-01; not compressed) (VOL-I-10.3-02; duration 5 WD is an ASSUMPTION: model_auditor_appointment)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -39395,12 +39772,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>I-A5-pcg-execution</t>
+          <t>I-A5-pcg-wording</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>A5 pcg-execution: INFEASIBLE by 4 WD (total float -4 WD: earliest start 2026-11-15 (after pcg-wording) is after the latest start 2026-11-09; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_execution)</t>
+          <t>A5 pcg-wording: INFEASIBLE by 4 WD (total float -4 WD: latest start 2026-10-26 is before the planning date 2026-11-01; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_wording)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -39423,17 +39800,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>I-A5-fin-model-freeze</t>
+          <t>I-A5-technical-proposal</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>A5 fin-model-freeze: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-23 (after fin-model-build) is after the latest start 2026-11-15; not compressed) (VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 1 WD is an ASSUMPTION: fin_model_freeze)</t>
+          <t>A5 technical-proposal: INFEASIBLE by 4 WD (total float -4 WD: latest start 2026-10-26 is before the planning date 2026-11-01; not compressed) (ADD-02-5.2-01, ADD-02-T1-1-N3-01, ADD-03-5.2-01, VOL-I-11.3-01, VOL-I-9.2-01, VOL-I-9.7-01, VOL-I-T1-1-A, VOL-I-T1-1-B, VOL-I-T1-1-C, VOL-I-T1-1-D, VOL-I-T1-1-E, VOL-I-T1-1-F, VOL-II-1.1-01, VOL-II-1.2-01, VOL-II-1.3-01, VOL-II-1.4-01, VOL-II-2.1-01, VOL-II-2.2-01, VOL-II-2.2-02, VOL-II-2.3-01, VOL-II-2.4-01, VOL-II-2.5-01, VOL-II-3.1-01, VOL-II-3.2-01, VOL-II-3.2-02, VOL-II-3.3-01, VOL-II-3.4-01, VOL-II-3.5-01, VOL-II-4.1-01, VOL-II-4.3-01, VOL-II-4.3-02, VOL-II-4.4-01, VOL-II-4.4-02, VOL-II-4.5-01, VOL-II-5.1-01, VOL-II-5.2-01, VOL-II-5.2-02, VOL-II-5.3-01, VOL-II-5.3-02, VOL-II-5.4-01, VOL-II-5.4-02, VOL-II-5.5-01, VOL-II-5.5-02, VOL-II-6.1-01, VOL-II-6.1-02, VOL-II-6.2-01, VOL-II-6.3-01, VOL-II-6.3-02, VOL-II-6.4-01, VOL-II-6.4-02, VOL-II-7.1-01, VOL-II-7.2-01, VOL-II-7.4-01, VOL-II-8.1-01, VOL-II-8.2-01, VOL-II-8.3-01, VOL-II-8.3-02, VOL-II-8.4-01, VOL-II-8.4-02, VOL-II-8.5-01, VOL-II-8.5-02, VOL-II-9.1-01, VOL-II-9.1-02, VOL-II-9.2-01, VOL-II-9.3-01, VOL-II-9.4-01, VOL-II-9.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-II-T2-6-1, VOL-II-T2-6-2, VOL-II-T2-6-3, VOL-II-T2-6-4, VOL-II-T2-6-5, VOL-II-T2-6-6; duration 20 WD is an ASSUMPTION: technical_proposal)</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -39443,7 +39820,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
+          <t>ADD-02-5.2-01; ADD-02-T1-1-N3-01; ADD-03-5.2-01; VOL-I-11.3-01; VOL-I-9.2-01; VOL-I-9.7-01; VOL-I-T1-1-A; VOL-I-T1-1-B; VOL-I-T1-1-C; VOL-I-T1-1-D; VOL-I-T1-1-E; VOL-I-T1-1-F; VOL-II-1.1-01; VOL-II-1.2-01; VOL-II-1.3-01; VOL-II-1.4-01; VOL-II-2.1-01; VOL-II-2.2-01; VOL-II-2.2-02; VOL-II-2.3-01; VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-3.1-01; VOL-II-3.2-01; VOL-II-3.2-02; VOL-II-3.3-01; VOL-II-3.4-01; VOL-II-3.5-01; VOL-II-4.1-01; VOL-II-4.3-01; VOL-II-4.3-02; VOL-II-4.4-01; VOL-II-4.4-02; VOL-II-4.5-01; VOL-II-5.1-01; VOL-II-5.2-01; VOL-II-5.2-02; VOL-II-5.3-01; VOL-II-5.3-02; VOL-II-5.4-01; VOL-II-5.4-02; VOL-II-5.5-01; VOL-II-5.5-02; VOL-II-6.1-01; VOL-II-6.1-02; VOL-II-6.2-01; VOL-II-6.3-01; VOL-II-6.3-02; VOL-II-6.4-01; VOL-II-6.4-02; VOL-II-7.1-01; VOL-II-7.2-01; VOL-II-7.4-01; VOL-II-8.1-01; VOL-II-8.2-01; VOL-II-8.3-01; VOL-II-8.3-02; VOL-II-8.4-01; VOL-II-8.4-02; VOL-II-8.5-01; VOL-II-8.5-02; VOL-II-9.1-01; VOL-II-9.1-02; VOL-II-9.2-01; VOL-II-9.3-01; VOL-II-9.4-01; VOL-II-9.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-3; VOL-II-T2-6-4; VOL-II-T2-6-5; VOL-II-T2-6-6</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -39451,12 +39828,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>I-A5-model-audit-opinion</t>
+          <t>I-A5-model-audit-review</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>A5 model-audit-opinion: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-24 (after fin-model-freeze) is after the latest start 2026-11-16; not compressed) (VOL-I-10.3-02; duration 5 WD is an ASSUMPTION: model_audit_opinion)</t>
+          <t>A5 model-audit-review: INFEASIBLE by 4 WD (total float -4 WD: earliest start 2026-11-08 (after model-auditor-appoint) is after the latest start 2026-11-02; not compressed) (VOL-I-10.3-02; duration 10 WD is an ASSUMPTION: model_audit_review)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -39479,17 +39856,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>I-A5-fin-assumptions</t>
+          <t>I-A5-pcg-execution</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>A5 fin-assumptions: INFEASIBLE by 2 WD (total float -2 WD: earliest start 2026-11-24 (after fin-model-freeze) is after the latest start 2026-11-19; not compressed) (VOL-I-10.6-01; duration 2 WD is an ASSUMPTION: fin_assumptions_schedule)</t>
+          <t>A5 pcg-execution: INFEASIBLE by 4 WD (total float -4 WD: earliest start 2026-11-15 (after pcg-wording) is after the latest start 2026-11-09; not compressed) (VOL-I-8.7-01, VOL-IV-F4D-01, VOL-IV-F4D-02, VOL-IV-F4D-03, VOL-IV-F4D-04, VOL-IV-F4D-05, VOL-IV-F4D-06, VOL-IV-F4D-07, VOL-IV-F4D-08; duration 10 WD is an ASSUMPTION: pcg_execution)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -39499,7 +39876,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.6-01</t>
+          <t>VOL-I-8.7-01; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -39507,12 +39884,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>I-A5-form-4f</t>
+          <t>I-A5-fin-model-freeze</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>A5 form-4f: INFEASIBLE by 2 WD (total float -2 WD: earliest start 2026-11-24 (after fin-model-freeze) is after the latest start 2026-11-19; not compressed) (VOL-I-10.1-01, VOL-I-10.2-01, VOL-I-10.4-01, VOL-I-10.5-01, VOL-IV-F4F-01, VOL-IV-F4F-02; duration 2 WD is an ASSUMPTION: form_4f_preparation)</t>
+          <t>A5 fin-model-freeze: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-23 (after fin-model-build) is after the latest start 2026-11-15; not compressed) (VOL-I-10.1-01, VOL-I-10.3-01, VOL-IV-F4F-02; duration 1 WD is an ASSUMPTION: fin_model_freeze)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -39527,7 +39904,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.4-01; VOL-I-10.5-01; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
+          <t>VOL-I-10.1-01; VOL-I-10.3-01; VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -39535,17 +39912,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-a</t>
+          <t>I-A5-model-audit-opinion</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-a: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-21 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 model-audit-opinion: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-11-24 (after fin-model-freeze) is after the latest start 2026-11-16; not compressed) (VOL-I-10.3-02; duration 5 WD is an ASSUMPTION: model_audit_opinion)</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -39555,7 +39932,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-10.3-02</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
@@ -39563,17 +39940,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-b</t>
+          <t>I-A5-fin-assumptions</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-b: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-12-01 (after model-audit-opinion) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 fin-assumptions: INFEASIBLE by 2 WD (total float -2 WD: earliest start 2026-11-24 (after fin-model-freeze) is after the latest start 2026-11-19; not compressed) (VOL-I-10.6-01; duration 2 WD is an ASSUMPTION: fin_assumptions_schedule)</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -39583,7 +39960,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-10.6-01</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr"/>
@@ -39591,17 +39968,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>I-A5-copies</t>
+          <t>I-A5-form-4f</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>A5 copies: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-22 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+          <t>A5 form-4f: INFEASIBLE by 2 WD (total float -2 WD: earliest start 2026-11-24 (after fin-model-freeze) is after the latest start 2026-11-19; not compressed) (VOL-I-10.1-01, VOL-I-10.2-01, VOL-I-10.4-01, VOL-I-10.5-01, VOL-IV-F4F-01, VOL-IV-F4F-02; duration 2 WD is an ASSUMPTION: form_4f_preparation)</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -39611,7 +39988,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.4-01; VOL-I-10.5-01; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
@@ -39619,12 +39996,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>I-A5-seal-and-mark</t>
+          <t>I-A5-assemble-envelope-a</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>A5 seal-and-mark: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-22 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+          <t>A5 assemble-envelope-a: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-21 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -39647,12 +40024,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>I-A5-deliver</t>
+          <t>I-A5-assemble-envelope-b</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>A5 deliver: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-23 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+          <t>A5 assemble-envelope-b: INFEASIBLE by 5 WD (total float -5 WD: earliest start 2026-12-01 (after model-audit-opinion) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -39675,12 +40052,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>I-A5-info-change-watch</t>
+          <t>I-A5-copies</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>A5 info-change-watch: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-4.2-02; duration 1 WD is an ASSUMPTION: info_change_notice)</t>
+          <t>A5 copies: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-22 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -39695,7 +40072,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-4.2-02</t>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
@@ -39703,12 +40080,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>I-A5-om-member-change-notice</t>
+          <t>I-A5-seal-and-mark</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>A5 om-member-change-notice: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-3.1-01, ADD-03-3.1-02, ADD-03-3.4-01; duration 1 WD is an ASSUMPTION: change_notice)</t>
+          <t>A5 seal-and-mark: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-22 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -39723,7 +40100,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>ADD-03-3.1-01; ADD-03-3.1-02; ADD-03-3.4-01</t>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr"/>
@@ -39731,33 +40108,117 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
+          <t>I-A5-deliver</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>A5 deliver: INFEASIBLE by 19 WD (total float -19 WD: earliest start 2026-12-23 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-info-change-watch</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>A5 info-change-watch: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-4.2-02; duration 1 WD is an ASSUMPTION: info_change_notice)</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03-4.2-02</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-om-member-change-notice</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>A5 om-member-change-notice: NO DEADLINE REACHED (not linked to a pack date) (ADD-03-3.1-01, ADD-03-3.1-02, ADD-03-3.4-01; duration 1 WD is an ASSUMPTION: change_notice)</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03-3.1-01; ADD-03-3.1-02; ADD-03-3.4-01</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 19 WD; lcc-certificate INFEASIBLE by 19 WD; fin-model-build INFEASIBLE by 5 WD; model-auditor-appoint INFEASIBLE by 4 WD; pcg-wording INFEASIBLE by 4 WD; technical-proposal INFEASIBLE by 4 WD; model-audit-review INFEASIBLE by 4 WD; pcg-execution INFEASIBLE by 4 WD; fin-model-freeze INFEASIBLE by 5 WD; model-audit-opinion INFEASIBLE by 5 WD; fin-assumptions INFEASIBLE by 2 WD; form-4f INFEASIBLE by 2 WD; assemble-envelope-a INFEASIBLE by 19 WD; assemble-envelope-b INFEASIBLE by 5 WD; copies INFEASIBLE by 19 WD; seal-and-mark INFEASIBLE by 19 WD; deliver INFEASIBLE by 19 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>ADD-02-5.2-01; ADD-02-T1-1-N3-01; ADD-03-5.2-01; VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.3-01; VOL-I-10.3-02; VOL-I-10.4-01; VOL-I-10.5-01; VOL-I-10.6-01; VOL-I-11.3-01; VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-8.6-01; VOL-I-8.7-01; VOL-I-9.1-01; VOL-I-9.2-01; VOL-I-9.7-01; VOL-I-App3-01; VOL-I-T1-1-A; VOL-I-T1-1-B; VOL-I-T1-1-C; VOL-I-T1-1-D; VOL-I-T1-1-E; VOL-I-T1-1-F; VOL-II-1.1-01; VOL-II-1.2-01; VOL-II-1.3-01; VOL-II-1.4-01; VOL-II-2.1-01; VOL-II-2.2-01; VOL-II-2.2-02; VOL-II-2.3-01; VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-3.1-01; VOL-II-3.2-01; VOL-II-3.2-02; VOL-II-3.3-01; VOL-II-3.4-01; VOL-II-3.5-01; VOL-II-4.1-01; VOL-II-4.3-01; VOL-II-4.3-02; VOL-II-4.4-01; VOL-II-4.4-02; VOL-II-4.5-01; VOL-II-5.1-01; VOL-II-5.2-01; VOL-II-5.2-02; VOL-II-5.3-01; VOL-II-5.3-02; VOL-II-5.4-01; VOL-II-5.4-02; VOL-II-5.5-01; VOL-II-5.5-02; VOL-II-6.1-01; VOL-II-6.1-02; VOL-II-6.2-01; VOL-II-6.3-01; VOL-II-6.3-02; VOL-II-6.4-01; VOL-II-6.4-02; VOL-II-7.1-01; VOL-II-7.2-01; VOL-II-7.4-01; VOL-II-8.1-01; VOL-II-8.2-01; VOL-II-8.3-01; VOL-II-8.3-02; VOL-II-8.4-01; VOL-II-8.4-02; VOL-II-8.5-01; VOL-II-8.5-02; VOL-II-9.1-01; VOL-II-9.1-02; VOL-II-9.2-01; VOL-II-9.3-01; VOL-II-9.4-01; VOL-II-9.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-3; VOL-II-T2-6-4; VOL-II-T2-6-5; VOL-II-T2-6-6; VOL-IV-F4D-01; VOL-IV-F4D-02; VOL-IV-F4D-03; VOL-IV-F4D-04; VOL-IV-F4D-05; VOL-IV-F4D-06; VOL-IV-F4D-07; VOL-IV-F4D-08; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F74"/>
+  <autoFilter ref="A1:F77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42955,4 +43416,1580 @@
   <autoFilter ref="A1:E51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Blocks</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Issues</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-FIN-STANDING</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.4-01; VOL-I-8.4-02; calc:financial-standing</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.4 p4: “on a combined basis across consortium members weighted by shareholding”; VOL-I:8.1 p4: “No change to the composition, shareholding or lead member of a prequalified consortium shall be effective without the prior written consent of the Authority.”</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>The financial standing is combined across the members and weighted by shareholding: a member added, removed or re-weighted changes the calculation (the members and their shares are bidder facts, I-BIDDER-FACTS).</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-FORM-4C</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-9.4-01; VOL-IV-F4C-N1</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:9.4 p5: “signed and stamped by an authorised signatory of each member of the Bidder”; VOL-I:9.4 p5: “Failure to submit a complete and properly executed Form 4-C for each member shall render the Proposal non-responsive.”; VOL-IV:F4-C/image/note p6: “يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف”</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>One Form 4-C per member: a new member gives its own (in Arabic, signed and stamped by its authorised signatory).</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-MULTIPLE-PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.2-01; VOL-IV-F4C-02</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.2 p4: “No firm, and no affiliate of a firm, shall participate in more than one Proposal.”; VOL-IV:F4-C/image/intro p6: “بصفتنا ممثلين مفوضين عن العضو المذكور أدناه في ائتلاف مقدم العرض”; VOL-IV:F4-C/image/decl2 p6: “أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة”</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Each member declares in its Form 4-C (declaration 2, given for 'the member named below') that it has not taken part in more than one proposal: a new member, and its affiliates, must be checked against VOL-I 8.2.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-DEBARMENT</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.10-01; VOL-IV-F4C-03</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.10 p4: “No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.”; VOL-I:8.10 p4: “A declaration to this effect shall be given in Form 4-C.”</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-INVESTMENT-LICENCE</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.9-01</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.9 p4: “evidence of a current investment licence for each foreign consortium member”</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Whether a new member is foreign is a bidder fact (bidder.foreign_members is a labelled assumption).</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>REL-ADD03-OM-OPERATOR-MEMBER</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.8</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-9.4-01; VOL-IV-F4C-N1; ADD-03-4.4-01; ADD-03-Q15-01; VOL-I-8.4-01; VOL-I-8.4-02; VOL-I-8.2-01; VOL-IV-F4C-02</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03:3.1 p1: “The proposed O&amp;M Operator shall be a member of the Bidder”; VOL-I:9.4 p5: “signed and stamped by an authorised signatory of each member of the Bidder”; ADD-03:4.4 p2: “Each member of the Bidder shall give the fourth declaration as substituted.”; ADD-03:Q15 p2: “A member incorporated outside the Kingdom shall attach an English translation to its Form 4-C.”; VOL-I:8.4 p4: “on a combined basis across consortium members weighted by shareholding”; VOL-IV:F4-C/image/decl2 p6: “أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة”</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>As a member, the O&amp;M Operator gives its own Form 4-C (with the substituted fourth declaration, and an English translation if incorporated outside the Kingdom), enters the shareholding-weighted financial standing, and is subject to VOL-I 8.2 with its affiliates.</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-PROCESS-DESIGN</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-3.1-01</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:3.1 p3: “The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditions in Table 2-2.”</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>A changed limit, unit or basis of assessment changes what the process design must achieve. The qualifier 'all values are maxima' and the chlorine and pH ranges stay an open question (I-VOL-II-T24-TENSIONS).</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-RELIABILITY-RUN</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-7.2-01</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:7.2 p4: “during which every parameter in Table 2-4 has been met”; VOL-II:7.3 p4: “A failure of any Table 2-4 parameter during the reliability run shall restart the run in full.”</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>The 30-day reliability run before PCOD must meet every Table 2-4 parameter as amended; a failure restarts it in full.</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-UNAVAILABILITY</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-02</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.1 p3: “(b) the treated effluent fails any parameter in Volume II Table 2-4”</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>After PCOD a failure of any Table 2-4 parameter is an Unavailability Event (VOL-V 31.1(b)), with deductions and no cure period.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-RAMP-UP-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.3-01</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.3 p3: “no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis”</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>The second limb of 29.3 turns on which parameters Table 2-4 assesses on a rolling average: a changed basis of assessment changes the Ramp-Up relief.</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-4.3-02</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “The treated effluent shall at all times comply with the parameters set out in Table 2-4.”; VOL-II:2.5 p2: “continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous basis”; VOL-II:4.3 p4: “such that the Facility can meet Table 2-4 with any one stream out of service”</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-MECHANISM</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-V:H:C29 p3: “CLAUSE 29 — PAYMENT MECHANISM”</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Every sub-clause of Clause 29 is part of the payment mechanism the Availability Payment is calculated under (the Ramp-Up payment of 29.3 included).</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>The definition says the Availability Payment is adjusted under Clause 31, but the price quoted under VOL-I 10.2 is calculated under Clause 29 only: whether a change to the deductions changes the quoted price, or only the risk priced into it, is a commercial judgement (inferred, not stated).</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-QUOTED-PRICE</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.2-01</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.2 p5: “The Bidder shall quote a single Availability Payment expressed in Saudi Riyals per annum, calculated in accordance with the payment mechanism at Volume V Clause 29.”</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FORM-4F</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV-F4F-01</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/availability-payment-sar-per-annum-year-1-of-operations p9: “Availability Payment (SAR per annum, year 1 of operations):”; VOL-IV:F4-F/indexation-basis-assumed p9: “Indexation basis assumed: Per Volume V Clause 29.2”</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FINANCIAL-MODEL</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/para1 p9: “has been derived from the Financial Model submitted with this Form”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Form 4-F states that the Availability Payment is derived from the Financial Model, and VOL-I 10.2 that it is calculated under the payment mechanism of Volume V Clause 29; so the model must reproduce Clause 29 (the Ramp-Up payment of 29.3 included). That a change to Clause 29 requires the model to be re-run is the curator's inference, not a stated link.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Reaches the Envelope B modelling activities (fin-model-build, fin-model-freeze) through the row's evidence item (EV-FIN-MODEL).</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>REL-MODEL-FORM-4F</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV-F4F-02</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/para1 p9: “We confirm that the Availability Payment stated above is unconditional, is not subject to any qualification, and has been derived from the Financial Model submitted with this Form.”</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FINANCING-ASSUMPTIONS</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>possible impact</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.6-01</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.6 p5: “a schedule of the principal financing assumptions underlying the Availability Payment”</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>The schedule states the financing assumptions underlying the Availability Payment; whether a change to the payment mechanism changes them (for example debt sized on the Ramp-Up revenue) is a commercial judgement.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-DEFAULTS</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-39.1-01</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “The Authority may terminate for a Project Company Event of Default, being the events listed in Schedule 11.”</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-LATE-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2 p2: “without prejudice to its termination rights under Clause 39”; VOL-V:39.1 p4: “being the events listed in Schedule 11”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V:39.3</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “being the events listed in Schedule 11”; VOL-V:31.4 p3: “on a second occurrence, to terminate under Clause 39.3”; VOL-V:39.3 p4: “The Authority may terminate for persistent breach in the circumstances described in Clause 31.4.”</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>31.4 and 39.3 give a termination right for persistent breach; 39.1 gives one for the Events of Default in Schedule 11, which is not supplied. The documents do not say whether persistent breach is also listed there: that it may be is the curator's inference.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING; I-VOL-V-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>ADD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-7-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2 p3: “the Authority shall deduct from the Availability Payment the amounts calculated under Schedule 7”</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 7 (deductions)</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-ENVIRONMENTAL-PERMIT</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4; VOL-II:T2-4-heading/para1</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “Table 2-4 is reproduced overleaf from the Environmental Permit issued for the site”; VOL-II:T2-4-heading/para1 p3: “In the event of any discrepancy between this reproduction and the Environmental Permit, the Environmental Permit shall prevail.”; VOL-II:T2-4/note1 p3: “Where a parameter is not listed above, the limit stated in the Environmental Permit shall apply.”</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>the Environmental Permit issued for the site</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>I-PERMIT</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02; ADD-03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>